--- a/artfynd/A 1383-2021 artfynd.xlsx
+++ b/artfynd/A 1383-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1383-2021 artfynd.xlsx
+++ b/artfynd/A 1383-2021 artfynd.xlsx
@@ -815,12 +815,7 @@
         <v>57089594</v>
       </c>
       <c r="B3" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -855,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346370.516971525</v>
+        <v>346371</v>
       </c>
       <c r="R3" t="n">
-        <v>6511405.235050795</v>
+        <v>6511405</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -888,19 +883,9 @@
           <t>1972-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1973-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 1383-2021 artfynd.xlsx
+++ b/artfynd/A 1383-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>57089594</v>
       </c>
       <c r="B3" t="n">
-        <v>104016</v>
+        <v>104028</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1383-2021 artfynd.xlsx
+++ b/artfynd/A 1383-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>57089594</v>
       </c>
       <c r="B3" t="n">
-        <v>104028</v>
+        <v>104036</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1383-2021 artfynd.xlsx
+++ b/artfynd/A 1383-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>57089594</v>
       </c>
       <c r="B3" t="n">
-        <v>104036</v>
+        <v>104048</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1383-2021 artfynd.xlsx
+++ b/artfynd/A 1383-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>57089594</v>
       </c>
       <c r="B3" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1383-2021 artfynd.xlsx
+++ b/artfynd/A 1383-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>57089594</v>
       </c>
       <c r="B3" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1383-2021 artfynd.xlsx
+++ b/artfynd/A 1383-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>57089594</v>
       </c>
       <c r="B3" t="n">
-        <v>104060</v>
+        <v>104087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1383-2021 artfynd.xlsx
+++ b/artfynd/A 1383-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>57089594</v>
       </c>
       <c r="B3" t="n">
-        <v>104087</v>
+        <v>104093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1383-2021 artfynd.xlsx
+++ b/artfynd/A 1383-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>57089594</v>
       </c>
       <c r="B3" t="n">
-        <v>104093</v>
+        <v>104100</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1383-2021 artfynd.xlsx
+++ b/artfynd/A 1383-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>57089594</v>
       </c>
       <c r="B3" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1383-2021 artfynd.xlsx
+++ b/artfynd/A 1383-2021 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>57089594</v>
       </c>
       <c r="B3" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1383-2021 artfynd.xlsx
+++ b/artfynd/A 1383-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>56040561</v>
       </c>
       <c r="B2" t="n">
-        <v>95754</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346474.1028206627</v>
+        <v>346474</v>
       </c>
       <c r="R2" t="n">
-        <v>6511271.661005465</v>
+        <v>6511272</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,19 +759,9 @@
           <t>2015-12-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-12-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 1383-2021 artfynd.xlsx
+++ b/artfynd/A 1383-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56040561</v>
       </c>
       <c r="B2" t="n">
-        <v>97839</v>
+        <v>97842</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1383-2021 artfynd.xlsx
+++ b/artfynd/A 1383-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56040561</v>
       </c>
       <c r="B2" t="n">
-        <v>97842</v>
+        <v>97871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1383-2021 artfynd.xlsx
+++ b/artfynd/A 1383-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56040561</v>
       </c>
       <c r="B2" t="n">
-        <v>97871</v>
+        <v>97883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1383-2021 artfynd.xlsx
+++ b/artfynd/A 1383-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56040561</v>
       </c>
       <c r="B2" t="n">
-        <v>97883</v>
+        <v>97884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1383-2021 artfynd.xlsx
+++ b/artfynd/A 1383-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56040561</v>
       </c>
       <c r="B2" t="n">
-        <v>97884</v>
+        <v>97889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1383-2021 artfynd.xlsx
+++ b/artfynd/A 1383-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56040561</v>
       </c>
       <c r="B2" t="n">
-        <v>97889</v>
+        <v>97893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1383-2021 artfynd.xlsx
+++ b/artfynd/A 1383-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56040561</v>
       </c>
       <c r="B2" t="n">
-        <v>97893</v>
+        <v>97895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1383-2021 artfynd.xlsx
+++ b/artfynd/A 1383-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56040561</v>
       </c>
       <c r="B2" t="n">
-        <v>97895</v>
+        <v>97905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
